--- a/resources/templates/standard/L1100-06.xlsx
+++ b/resources/templates/standard/L1100-06.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>설비 고장 조치 보고서</t>
   </si>
@@ -876,13 +879,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -965,7 +970,7 @@
     </row>
     <row r="3" ht="17.15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -982,7 +987,7 @@
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
       <c r="P3" s="10" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q3" s="10"/>
       <c r="R3" s="10"/>
@@ -1012,7 +1017,7 @@
     </row>
     <row r="4" ht="17.15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1029,7 +1034,7 @@
       <c r="N4" s="12"/>
       <c r="O4" s="12"/>
       <c r="P4" s="13" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q4" s="13"/>
       <c r="R4" s="13"/>
@@ -1059,7 +1064,7 @@
     </row>
     <row r="5" ht="17.15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -1076,7 +1081,7 @@
       <c r="N5" s="12"/>
       <c r="O5" s="12"/>
       <c r="P5" s="13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q5" s="13"/>
       <c r="R5" s="13"/>
@@ -1106,7 +1111,7 @@
     </row>
     <row r="6" ht="17.15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -1123,7 +1128,7 @@
       <c r="N6" s="12"/>
       <c r="O6" s="12"/>
       <c r="P6" s="13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q6" s="13"/>
       <c r="R6" s="13"/>
@@ -1153,7 +1158,7 @@
     </row>
     <row r="7" ht="17.15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -1175,7 +1180,7 @@
       <c r="S7" s="14"/>
       <c r="T7" s="14"/>
       <c r="U7" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V7" s="15"/>
       <c r="W7" s="15"/>
@@ -1200,11 +1205,11 @@
     </row>
     <row r="8" ht="17.15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
@@ -1335,7 +1340,7 @@
       <c r="A11" s="16"/>
       <c r="B11" s="16"/>
       <c r="C11" s="17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" s="17"/>
       <c r="E11" s="17"/>
@@ -1466,7 +1471,7 @@
       <c r="A14" s="16"/>
       <c r="B14" s="16"/>
       <c r="C14" s="22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="22"/>
@@ -1595,7 +1600,7 @@
     </row>
     <row r="17" ht="17.15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="16"/>
       <c r="C17" s="24"/>
@@ -1812,11 +1817,11 @@
     </row>
     <row r="22" ht="17.15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
@@ -2031,11 +2036,11 @@
     </row>
     <row r="27" ht="17.15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
@@ -2060,16 +2065,16 @@
       <c r="X27" s="13"/>
       <c r="Y27" s="13"/>
       <c r="Z27" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA27" s="13"/>
       <c r="AB27" s="13"/>
       <c r="AC27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD27" s="13"/>
       <c r="AE27" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF27" s="13"/>
       <c r="AG27" s="13"/>
@@ -2086,7 +2091,7 @@
       <c r="A28" s="16"/>
       <c r="B28" s="16"/>
       <c r="C28" s="17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
@@ -2217,7 +2222,7 @@
       <c r="A31" s="16"/>
       <c r="B31" s="16"/>
       <c r="C31" s="22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
@@ -2348,7 +2353,7 @@
       <c r="A34" s="16"/>
       <c r="B34" s="16"/>
       <c r="C34" s="41" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D34" s="41"/>
       <c r="E34" s="41"/>
@@ -2434,7 +2439,7 @@
     </row>
     <row r="36" ht="17.15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="42"/>
@@ -2945,19 +2950,19 @@
       <c r="AI47" s="5"/>
       <c r="AJ47" s="5"/>
       <c r="AK47" s="46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL47" s="47" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM47" s="47" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AN47" s="47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AO47" s="47" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:41" x14ac:dyDescent="0.25">
